--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CEMALU ALDAIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CEMALU ALDAIA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>102.9015</v>
+        <v>78.4765</v>
       </c>
       <c r="E2" t="n">
-        <v>90.09180000000001</v>
+        <v>71.5093</v>
       </c>
       <c r="F2" t="n">
-        <v>12.8095</v>
+        <v>6.966600000000001</v>
       </c>
       <c r="G2" t="n">
         <v>21.935</v>
@@ -610,13 +610,13 @@
         <v>57.9095</v>
       </c>
       <c r="S2" t="n">
-        <v>33.4053</v>
+        <v>8.9802</v>
       </c>
       <c r="T2" t="n">
-        <v>22.6294</v>
+        <v>4.0469</v>
       </c>
       <c r="U2" t="n">
-        <v>10.7759</v>
+        <v>4.933</v>
       </c>
       <c r="V2" t="n">
         <v>51.7757</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CARRION BALLESTER</t>
+          <t>J. CARPIO MAÑEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.587099999999999</v>
+        <v>1.9004</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7116</v>
+        <v>1.9004</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8758</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.938999999999999</v>
+        <v>1.9004</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1091000000000004</v>
+        <v>0.6502</v>
       </c>
       <c r="I3" t="n">
-        <v>2.829800000000001</v>
+        <v>1.2502</v>
       </c>
       <c r="J3" t="n">
-        <v>12.6452</v>
+        <v>1.9004</v>
       </c>
       <c r="K3" t="n">
-        <v>8.6273</v>
+        <v>0.6502</v>
       </c>
       <c r="L3" t="n">
-        <v>4.018</v>
+        <v>1.2502</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.706199999999999</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-8.517900000000001</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1882</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9164000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-18.6923</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>17.7761</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4859</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0154</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4704</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.9213</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5.743</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CARPIO MAÑEZ</t>
+          <t>D. OLID SANGÜESA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,34 +718,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9004</v>
+        <v>1.2753</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9004</v>
+        <v>1.2753</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9004</v>
+        <v>1.2753</v>
       </c>
       <c r="H4" t="n">
         <v>0.6502</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2502</v>
+        <v>0.6251</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9004</v>
+        <v>1.2753</v>
       </c>
       <c r="K4" t="n">
         <v>0.6502</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2502</v>
+        <v>0.6251</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. OLID SANGÜESA</t>
+          <t>A. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2753</v>
+        <v>0.9766000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2753</v>
+        <v>0.1324999999999992</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.8439999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2753</v>
+        <v>2.938999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6502</v>
+        <v>0.1091000000000004</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6251</v>
+        <v>2.829800000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2753</v>
+        <v>12.6452</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6502</v>
+        <v>8.6273</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6251</v>
+        <v>4.018</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-9.706199999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-8.517900000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.1882</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.9164000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-18.6923</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>17.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.8751</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.4365000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.4390000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.9213</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>5.743</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-7.6642</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7466000000000002</v>
+        <v>0.3001999999999996</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3392999999999998</v>
+        <v>1.4109</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0859</v>
+        <v>-1.1106</v>
       </c>
       <c r="G6" t="n">
         <v>0.7312999999999998</v>
@@ -922,13 +922,13 @@
         <v>6.5972</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9493</v>
+        <v>0.09730000000000008</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0121</v>
+        <v>0.05950000000000003</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.03779999999999997</v>
       </c>
       <c r="V6" t="n">
         <v>-2.5443</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.0929</v>
+        <v>-4.8758</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2032</v>
+        <v>-1.0109</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.8897</v>
+        <v>-3.8649</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1275</v>
@@ -1000,13 +1000,13 @@
         <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6984</v>
+        <v>-0.4813</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3681</v>
+        <v>-0.3433</v>
       </c>
       <c r="V7" t="n">
         <v>-2.5339</v>
@@ -1033,13 +1033,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.9219</v>
+        <v>-4.968999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08530000000000015</v>
+        <v>0.1069000000000004</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.8365</v>
+        <v>-5.0761</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0591</v>
@@ -1078,13 +1078,13 @@
         <v>3.6651</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.5672</v>
+        <v>-1.6142</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.031</v>
+        <v>-0.8386</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.5362</v>
+        <v>-0.7757000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-2.2121</v>
@@ -1111,13 +1111,13 @@
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>-10.2379</v>
+        <v>-6.243399999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.154199999999999</v>
+        <v>-6.1595</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0834</v>
+        <v>-0.08389999999999975</v>
       </c>
       <c r="G9" t="n">
         <v>-4.9529</v>
@@ -1156,13 +1156,13 @@
         <v>7.5135</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.9932</v>
+        <v>-1.9989</v>
       </c>
       <c r="T9" t="n">
-        <v>-4.0755</v>
+        <v>-1.0804</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.9179</v>
+        <v>-0.9184</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6742</v>
@@ -1189,13 +1189,13 @@
         <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>-11.1556</v>
+        <v>-7.1868</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7358</v>
+        <v>0.1397999999999984</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.419700000000001</v>
+        <v>-7.3267</v>
       </c>
       <c r="G10" t="n">
         <v>7.7515</v>
@@ -1234,13 +1234,13 @@
         <v>34.6355</v>
       </c>
       <c r="S10" t="n">
-        <v>-10.8078</v>
+        <v>-6.8395</v>
       </c>
       <c r="T10" t="n">
-        <v>-7.912100000000001</v>
+        <v>-4.0365</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.8958</v>
+        <v>-2.8029</v>
       </c>
       <c r="V10" t="n">
         <v>3.446200000000001</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SOLBES SORIANO</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.374</v>
+        <v>-11.9907</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8219999999999998</v>
+        <v>-6.761899999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.196</v>
+        <v>-5.228700000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-10.9537</v>
+        <v>-14.4227</v>
       </c>
       <c r="H11" t="n">
-        <v>-8.5463</v>
+        <v>-19.4125</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4072</v>
+        <v>4.9899</v>
       </c>
       <c r="J11" t="n">
-        <v>10.1437</v>
+        <v>22.823</v>
       </c>
       <c r="K11" t="n">
-        <v>7.994499999999999</v>
+        <v>12.4084</v>
       </c>
       <c r="L11" t="n">
-        <v>2.1487</v>
+        <v>10.4147</v>
       </c>
       <c r="M11" t="n">
-        <v>-21.0968</v>
+        <v>-37.2458</v>
       </c>
       <c r="N11" t="n">
-        <v>-16.541</v>
+        <v>-31.8211</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.556</v>
+        <v>-5.4247</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5497000000000002</v>
+        <v>2.749</v>
       </c>
       <c r="Q11" t="n">
-        <v>-23.8235</v>
+        <v>-41.5997</v>
       </c>
       <c r="R11" t="n">
-        <v>23.2736</v>
+        <v>44.3482</v>
       </c>
       <c r="S11" t="n">
-        <v>3.552999999999999</v>
+        <v>-9.8588</v>
       </c>
       <c r="T11" t="n">
-        <v>7.4293</v>
+        <v>-4.5399</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.8764</v>
+        <v>-5.3191</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.424</v>
+        <v>9.541799999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>7.0723</v>
+        <v>16.5537</v>
       </c>
       <c r="X11" t="n">
-        <v>-11.4962</v>
+        <v>-7.0119</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.1701</v>
+        <v>-12.8837</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.6646</v>
+        <v>-8.345599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.505500000000001</v>
+        <v>-4.537999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-9.2498</v>
@@ -1390,13 +1390,13 @@
         <v>8.0634</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.3105</v>
+        <v>-3.0242</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.0156</v>
+        <v>-1.6967</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2948</v>
+        <v>-1.3274</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9763000000000002</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SANCHEZ DE LA IGLESIA</t>
+          <t>A. SOLBES SORIANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.2646</v>
+        <v>-15.228</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.1174</v>
+        <v>-3.999000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.1472</v>
+        <v>-11.2291</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.540999999999999</v>
+        <v>-10.9537</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.8695</v>
+        <v>-8.5463</v>
       </c>
       <c r="I13" t="n">
-        <v>7.328399999999999</v>
+        <v>-2.4072</v>
       </c>
       <c r="J13" t="n">
-        <v>9.042</v>
+        <v>10.1437</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7489</v>
+        <v>7.994499999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>3.293</v>
+        <v>2.1487</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.5831</v>
+        <v>-21.0968</v>
       </c>
       <c r="N13" t="n">
-        <v>-17.6183</v>
+        <v>-16.541</v>
       </c>
       <c r="O13" t="n">
-        <v>4.0352</v>
+        <v>-4.556</v>
       </c>
       <c r="P13" t="n">
-        <v>7.5135</v>
+        <v>-0.5497000000000002</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.7446</v>
+        <v>-23.8235</v>
       </c>
       <c r="R13" t="n">
-        <v>21.2577</v>
+        <v>23.2736</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.4071</v>
+        <v>0.6991000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.0797</v>
+        <v>2.6086</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3274</v>
+        <v>-1.9093</v>
       </c>
       <c r="V13" t="n">
-        <v>-14.8298</v>
+        <v>-4.424</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6646</v>
+        <v>7.0723</v>
       </c>
       <c r="X13" t="n">
-        <v>-15.4946</v>
+        <v>-11.4962</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>A. SANCHEZ DE LA IGLESIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>-25.7419</v>
+        <v>-15.8637</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.3807</v>
+        <v>-6.478400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-19.3612</v>
+        <v>-9.385199999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.8094</v>
+        <v>-4.540999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.121600000000001</v>
+        <v>-11.8695</v>
       </c>
       <c r="I14" t="n">
-        <v>4.312399999999999</v>
+        <v>7.328399999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>22.2144</v>
+        <v>9.042</v>
       </c>
       <c r="K14" t="n">
-        <v>14.1456</v>
+        <v>5.7489</v>
       </c>
       <c r="L14" t="n">
-        <v>8.0688</v>
+        <v>3.293</v>
       </c>
       <c r="M14" t="n">
-        <v>-25.0238</v>
+        <v>-13.5831</v>
       </c>
       <c r="N14" t="n">
-        <v>-21.2672</v>
+        <v>-17.6183</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7565</v>
+        <v>4.0352</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3667000000000007</v>
+        <v>7.5135</v>
       </c>
       <c r="Q14" t="n">
-        <v>-38.1177</v>
+        <v>-13.7446</v>
       </c>
       <c r="R14" t="n">
-        <v>37.7506</v>
+        <v>21.2577</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8021</v>
+        <v>-4.0064</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4363</v>
+        <v>-2.4411</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.2387</v>
+        <v>-1.5654</v>
       </c>
       <c r="V14" t="n">
-        <v>-20.7639</v>
+        <v>-14.8298</v>
       </c>
       <c r="W14" t="n">
-        <v>6.0857</v>
+        <v>0.6646</v>
       </c>
       <c r="X14" t="n">
-        <v>-26.8496</v>
+        <v>-15.4946</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. CABRERA GONZALEZ</t>
+          <t>M. CISNEROS RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-28.6538</v>
+        <v>-21.984</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.6147</v>
+        <v>-13.8074</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.039</v>
+        <v>-8.1768</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.3862</v>
+        <v>-17.9678</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.1331</v>
+        <v>-10.5557</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.253</v>
+        <v>-7.412100000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.5933</v>
+        <v>0.5188000000000006</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.8168</v>
+        <v>4.977799999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.777</v>
+        <v>-4.459199999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.7928</v>
+        <v>-18.4866</v>
       </c>
       <c r="N15" t="n">
-        <v>-6.3165</v>
+        <v>-15.5336</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4763</v>
+        <v>-2.9528</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.5656</v>
+        <v>13.7445</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.2941</v>
+        <v>-11.9119</v>
       </c>
       <c r="R15" t="n">
-        <v>11.7286</v>
+        <v>25.6559</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9560999999999998</v>
+        <v>-6.6585</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9849</v>
+        <v>-4.0242</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.9415</v>
+        <v>-2.6345</v>
       </c>
       <c r="V15" t="n">
-        <v>-11.7456</v>
+        <v>-11.1014</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2879</v>
+        <v>1.6097</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.0333</v>
+        <v>-12.7112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-29.2076</v>
+        <v>-27.0811</v>
       </c>
       <c r="E16" t="n">
-        <v>-17.7118</v>
+        <v>-10.4719</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.4956</v>
+        <v>-16.6087</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.4227</v>
+        <v>-2.8094</v>
       </c>
       <c r="H16" t="n">
-        <v>-19.4125</v>
+        <v>-7.121600000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>4.9899</v>
+        <v>4.312399999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>22.823</v>
+        <v>22.2144</v>
       </c>
       <c r="K16" t="n">
-        <v>12.4084</v>
+        <v>14.1456</v>
       </c>
       <c r="L16" t="n">
-        <v>10.4147</v>
+        <v>8.0688</v>
       </c>
       <c r="M16" t="n">
-        <v>-37.2458</v>
+        <v>-25.0238</v>
       </c>
       <c r="N16" t="n">
-        <v>-31.8211</v>
+        <v>-21.2672</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.4247</v>
+        <v>-3.7565</v>
       </c>
       <c r="P16" t="n">
-        <v>2.749</v>
+        <v>-0.3667000000000007</v>
       </c>
       <c r="Q16" t="n">
-        <v>-41.5997</v>
+        <v>-38.1177</v>
       </c>
       <c r="R16" t="n">
-        <v>44.3482</v>
+        <v>37.7506</v>
       </c>
       <c r="S16" t="n">
-        <v>-27.0756</v>
+        <v>-3.1414</v>
       </c>
       <c r="T16" t="n">
-        <v>-15.4897</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-11.5858</v>
+        <v>-2.4859</v>
       </c>
       <c r="V16" t="n">
-        <v>9.541799999999999</v>
+        <v>-20.7639</v>
       </c>
       <c r="W16" t="n">
-        <v>16.5537</v>
+        <v>6.0857</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.0119</v>
+        <v>-26.8496</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CISNEROS RUIZ</t>
+          <t>S. CABRERA GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-32.3205</v>
+        <v>-29.7277</v>
       </c>
       <c r="E17" t="n">
-        <v>-19.4813</v>
+        <v>-18.4826</v>
       </c>
       <c r="F17" t="n">
-        <v>-12.8394</v>
+        <v>-11.2449</v>
       </c>
       <c r="G17" t="n">
-        <v>-17.9678</v>
+        <v>-13.3862</v>
       </c>
       <c r="H17" t="n">
-        <v>-10.5557</v>
+        <v>-10.1331</v>
       </c>
       <c r="I17" t="n">
-        <v>-7.412100000000001</v>
+        <v>-3.253</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5188000000000006</v>
+        <v>-5.5933</v>
       </c>
       <c r="K17" t="n">
-        <v>4.977799999999999</v>
+        <v>-3.8168</v>
       </c>
       <c r="L17" t="n">
-        <v>-4.459199999999999</v>
+        <v>-1.777</v>
       </c>
       <c r="M17" t="n">
-        <v>-18.4866</v>
+        <v>-7.7928</v>
       </c>
       <c r="N17" t="n">
-        <v>-15.5336</v>
+        <v>-6.3165</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.9528</v>
+        <v>-1.4763</v>
       </c>
       <c r="P17" t="n">
-        <v>13.7445</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q17" t="n">
-        <v>-11.9119</v>
+        <v>-14.2941</v>
       </c>
       <c r="R17" t="n">
-        <v>25.6559</v>
+        <v>11.7286</v>
       </c>
       <c r="S17" t="n">
-        <v>-16.9956</v>
+        <v>-2.0304</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.6982</v>
+        <v>0.1167999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-7.2972</v>
+        <v>-2.1473</v>
       </c>
       <c r="V17" t="n">
-        <v>-11.1014</v>
+        <v>-11.7456</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6097</v>
+        <v>1.2879</v>
       </c>
       <c r="X17" t="n">
-        <v>-12.7112</v>
+        <v>-13.0333</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>-34.533</v>
+        <v>-31.0485</v>
       </c>
       <c r="E18" t="n">
-        <v>-40.9533</v>
+        <v>-38.741</v>
       </c>
       <c r="F18" t="n">
-        <v>6.4204</v>
+        <v>7.6926</v>
       </c>
       <c r="G18" t="n">
         <v>-24.2665</v>
@@ -1858,13 +1858,13 @@
         <v>20.1583</v>
       </c>
       <c r="S18" t="n">
-        <v>-5.0084</v>
+        <v>-1.524</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.1696</v>
+        <v>-0.9571999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.8388</v>
+        <v>-0.5668</v>
       </c>
       <c r="V18" t="n">
         <v>-3.2422</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. MARI LOPEZ-ROCA</t>
+          <t>M. GONZALEZ BRU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>-46.6479</v>
+        <v>-43.3576</v>
       </c>
       <c r="E19" t="n">
-        <v>-43.8941</v>
+        <v>-23.6616</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7536</v>
+        <v>-19.6958</v>
       </c>
       <c r="G19" t="n">
-        <v>-42.8054</v>
+        <v>-13.2899</v>
       </c>
       <c r="H19" t="n">
-        <v>-24.4239</v>
+        <v>-8.1226</v>
       </c>
       <c r="I19" t="n">
-        <v>-18.3813</v>
+        <v>-5.167199999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-17.9287</v>
+        <v>6.4571</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.052200000000001</v>
+        <v>8.063599999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-10.8764</v>
+        <v>-1.6066</v>
       </c>
       <c r="M19" t="n">
-        <v>-24.8772</v>
+        <v>-19.747</v>
       </c>
       <c r="N19" t="n">
-        <v>-17.3717</v>
+        <v>-16.1861</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.5054</v>
+        <v>-3.5607</v>
       </c>
       <c r="P19" t="n">
-        <v>5.3144</v>
+        <v>-14.1107</v>
       </c>
       <c r="Q19" t="n">
-        <v>-26.9391</v>
+        <v>-30.4206</v>
       </c>
       <c r="R19" t="n">
-        <v>32.2534</v>
+        <v>16.31</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.335</v>
+        <v>-6.901</v>
       </c>
       <c r="T19" t="n">
-        <v>-3.8246</v>
+        <v>-3.8731</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.5102</v>
+        <v>-3.0281</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.8216</v>
+        <v>-9.0556</v>
       </c>
       <c r="W19" t="n">
-        <v>4.798</v>
+        <v>4.1747</v>
       </c>
       <c r="X19" t="n">
-        <v>-8.6196</v>
+        <v>-13.2306</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BRU</t>
+          <t>H. MARI LOPEZ-ROCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>-47.4752</v>
+        <v>-45.3944</v>
       </c>
       <c r="E20" t="n">
-        <v>-26.2174</v>
+        <v>-42.0927</v>
       </c>
       <c r="F20" t="n">
-        <v>-21.258</v>
+        <v>-3.302000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-13.2899</v>
+        <v>-42.8054</v>
       </c>
       <c r="H20" t="n">
-        <v>-8.1226</v>
+        <v>-24.4239</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.167199999999999</v>
+        <v>-18.3813</v>
       </c>
       <c r="J20" t="n">
-        <v>6.4571</v>
+        <v>-17.9287</v>
       </c>
       <c r="K20" t="n">
-        <v>8.063599999999999</v>
+        <v>-7.052200000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.6066</v>
+        <v>-10.8764</v>
       </c>
       <c r="M20" t="n">
-        <v>-19.747</v>
+        <v>-24.8772</v>
       </c>
       <c r="N20" t="n">
-        <v>-16.1861</v>
+        <v>-17.3717</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.5607</v>
+        <v>-7.5054</v>
       </c>
       <c r="P20" t="n">
-        <v>-14.1107</v>
+        <v>5.3144</v>
       </c>
       <c r="Q20" t="n">
-        <v>-30.4206</v>
+        <v>-26.9391</v>
       </c>
       <c r="R20" t="n">
-        <v>16.31</v>
+        <v>32.2534</v>
       </c>
       <c r="S20" t="n">
-        <v>-11.0191</v>
+        <v>-4.0818</v>
       </c>
       <c r="T20" t="n">
-        <v>-6.4289</v>
+        <v>-2.0233</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.59</v>
+        <v>-2.0585</v>
       </c>
       <c r="V20" t="n">
-        <v>-9.0556</v>
+        <v>-3.8216</v>
       </c>
       <c r="W20" t="n">
-        <v>4.1747</v>
+        <v>4.798</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.2306</v>
+        <v>-8.6196</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>-83.7383</v>
+        <v>-76.5899</v>
       </c>
       <c r="E21" t="n">
-        <v>-73.81399999999999</v>
+        <v>-68.8947</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.924099999999999</v>
+        <v>-7.6951</v>
       </c>
       <c r="G21" t="n">
         <v>-50.3441</v>
@@ -2092,13 +2092,13 @@
         <v>46.9137</v>
       </c>
       <c r="S21" t="n">
-        <v>-15.3967</v>
+        <v>-8.2484</v>
       </c>
       <c r="T21" t="n">
-        <v>-10.3079</v>
+        <v>-5.3884</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.0891</v>
+        <v>-2.8596</v>
       </c>
       <c r="V21" t="n">
         <v>-5.3526</v>
@@ -2125,13 +2125,13 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-297.6175</v>
+        <v>-271.4953</v>
       </c>
       <c r="E22" t="n">
-        <v>-181.8874</v>
+        <v>-172.4321</v>
       </c>
       <c r="F22" t="n">
-        <v>-115.7291</v>
+        <v>-99.06329999999998</v>
       </c>
       <c r="G22" t="n">
         <v>-175.6435</v>
@@ -2158,7 +2158,7 @@
         <v>-262.7537</v>
       </c>
       <c r="O22" t="n">
-        <v>-48.1472</v>
+        <v>-48.14720000000001</v>
       </c>
       <c r="P22" t="n">
         <v>-14.6605</v>
@@ -2170,13 +2170,13 @@
         <v>415.9936</v>
       </c>
       <c r="S22" t="n">
-        <v>-75.87790000000001</v>
+        <v>-49.75710000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-33.87989999999999</v>
+        <v>-24.4238</v>
       </c>
       <c r="U22" t="n">
-        <v>-41.99889999999999</v>
+        <v>-25.3324</v>
       </c>
       <c r="V22" t="n">
         <v>-31.4351</v>
